--- a/Results_experiment/exp_1/preds_1111113333322222.xlsx
+++ b/Results_experiment/exp_1/preds_1111113333322222.xlsx
@@ -990,7 +990,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D2">
-        <v>0.3987890183925629</v>
+        <v>-0.5563231706619263</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1004,7 +1004,7 @@
         <v>4.5</v>
       </c>
       <c r="D3">
-        <v>-0.4099175035953522</v>
+        <v>-1.322171926498413</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1018,7 +1018,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D4">
-        <v>-2.194824457168579</v>
+        <v>-3.118046998977661</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1032,7 +1032,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D5">
-        <v>-2.778108835220337</v>
+        <v>-4.019994258880615</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1046,7 +1046,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D6">
-        <v>-0.5162433981895447</v>
+        <v>1.251163721084595</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1060,7 +1060,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D7">
-        <v>0.9975715279579163</v>
+        <v>0.6735114455223083</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1074,7 +1074,7 @@
         <v>-3</v>
       </c>
       <c r="D8">
-        <v>1.760859608650208</v>
+        <v>1.577039480209351</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1088,7 +1088,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D9">
-        <v>9.622875213623047</v>
+        <v>10.76198673248291</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1102,7 +1102,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>2.467462539672852</v>
+        <v>1.987267255783081</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1116,7 +1116,7 @@
         <v>2.5</v>
       </c>
       <c r="D11">
-        <v>1.146691679954529</v>
+        <v>0.6536689400672913</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1130,7 +1130,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D12">
-        <v>2.599214315414429</v>
+        <v>2.066949844360352</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1144,7 +1144,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D13">
-        <v>-1.981188774108887</v>
+        <v>-2.417666673660278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1158,7 +1158,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D14">
-        <v>0.1689287126064301</v>
+        <v>-0.867024302482605</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1172,7 +1172,7 @@
         <v>6.5</v>
       </c>
       <c r="D15">
-        <v>3.049674987792969</v>
+        <v>2.529933929443359</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1186,7 +1186,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D16">
-        <v>2.906535148620605</v>
+        <v>3.121858358383179</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1200,7 +1200,7 @@
         <v>-7.599999904632568</v>
       </c>
       <c r="D17">
-        <v>-4.949731349945068</v>
+        <v>-4.106716156005859</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1214,7 +1214,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D18">
-        <v>2.261955261230469</v>
+        <v>1.726708173751831</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1228,7 +1228,7 @@
         <v>-13.60000038146973</v>
       </c>
       <c r="D19">
-        <v>-6.426330089569092</v>
+        <v>-8.397524833679199</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1242,7 +1242,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D20">
-        <v>2.067649602890015</v>
+        <v>0.9030933976173401</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1256,7 +1256,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D21">
-        <v>0.2037804424762726</v>
+        <v>-1.197830200195312</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1270,7 +1270,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D22">
-        <v>-1.526459932327271</v>
+        <v>-2.261188507080078</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1284,7 +1284,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D23">
-        <v>-3.143333911895752</v>
+        <v>-3.029054641723633</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1298,7 +1298,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D24">
-        <v>-3.683829784393311</v>
+        <v>-3.0520920753479</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1312,7 +1312,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D25">
-        <v>0.1639867424964905</v>
+        <v>-1.036919116973877</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1326,7 +1326,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D26">
-        <v>3.08272910118103</v>
+        <v>2.866420030593872</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1340,7 +1340,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D27">
-        <v>0.6619577407836914</v>
+        <v>-0.9893882870674133</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1354,7 +1354,7 @@
         <v>-2</v>
       </c>
       <c r="D28">
-        <v>1.755097270011902</v>
+        <v>-0.6368075609207153</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1368,7 +1368,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D29">
-        <v>-2.271169662475586</v>
+        <v>-2.075587749481201</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1382,7 +1382,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D30">
-        <v>3.272480964660645</v>
+        <v>3.02445650100708</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1396,7 +1396,7 @@
         <v>1.5</v>
       </c>
       <c r="D31">
-        <v>1.903759479522705</v>
+        <v>2.176340818405151</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1410,7 +1410,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D32">
-        <v>-2.99404764175415</v>
+        <v>-3.694491147994995</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1424,7 +1424,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D33">
-        <v>2.78429126739502</v>
+        <v>2.430176973342896</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1438,7 +1438,7 @@
         <v>-10.19999980926514</v>
       </c>
       <c r="D34">
-        <v>-3.683516263961792</v>
+        <v>-3.37773060798645</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1452,7 +1452,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D35">
-        <v>-4.286402702331543</v>
+        <v>-3.525160074234009</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1466,7 +1466,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D36">
-        <v>2.967933177947998</v>
+        <v>3.113578081130981</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1480,7 +1480,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D37">
-        <v>2.607481718063354</v>
+        <v>2.686236619949341</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1494,7 +1494,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D38">
-        <v>-3.140703201293945</v>
+        <v>-2.819164037704468</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1508,7 +1508,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D39">
-        <v>-1.990075349807739</v>
+        <v>-2.39067816734314</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1522,7 +1522,7 @@
         <v>-1</v>
       </c>
       <c r="D40">
-        <v>2.06763219833374</v>
+        <v>1.46082067489624</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1536,7 +1536,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D41">
-        <v>4.133056163787842</v>
+        <v>3.165160417556763</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1550,7 +1550,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D42">
-        <v>2.937877893447876</v>
+        <v>2.246674776077271</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1564,7 +1564,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D43">
-        <v>2.998801708221436</v>
+        <v>2.475656270980835</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1578,7 +1578,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D44">
-        <v>-2.8262038230896</v>
+        <v>-2.59822678565979</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1592,7 +1592,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D45">
-        <v>-1.563693761825562</v>
+        <v>-1.169476270675659</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1606,7 +1606,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D46">
-        <v>-2.164679527282715</v>
+        <v>-2.581281900405884</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1620,7 +1620,7 @@
         <v>-19.5</v>
       </c>
       <c r="D47">
-        <v>-17.32487869262695</v>
+        <v>-17.31373977661133</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1634,7 +1634,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D48">
-        <v>-2.251408338546753</v>
+        <v>-2.376328706741333</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1648,7 +1648,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D49">
-        <v>-3.13834023475647</v>
+        <v>-3.331891059875488</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1662,7 +1662,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D50">
-        <v>0.9356788992881775</v>
+        <v>0.2351576089859009</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1676,7 +1676,7 @@
         <v>-10.80000019073486</v>
       </c>
       <c r="D51">
-        <v>-11.03598403930664</v>
+        <v>-10.34394645690918</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1690,7 +1690,7 @@
         <v>-16.10000038146973</v>
       </c>
       <c r="D52">
-        <v>-13.43111038208008</v>
+        <v>-13.8916597366333</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1704,7 +1704,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D53">
-        <v>0.111531637609005</v>
+        <v>0.4611518979072571</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1718,7 +1718,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D54">
-        <v>-3.464102745056152</v>
+        <v>-4.194084167480469</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1732,7 +1732,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D55">
-        <v>2.849247932434082</v>
+        <v>2.775463342666626</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1746,7 +1746,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D56">
-        <v>-3.155332088470459</v>
+        <v>-3.76459002494812</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1760,7 +1760,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D57">
-        <v>-3.077333927154541</v>
+        <v>-2.181796073913574</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1774,7 +1774,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D58">
-        <v>1.188906788825989</v>
+        <v>0.06236463785171509</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1788,7 +1788,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D59">
-        <v>2.232481002807617</v>
+        <v>1.024223804473877</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1802,7 +1802,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D60">
-        <v>0.3618886768817902</v>
+        <v>-0.1239289790391922</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1816,7 +1816,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D61">
-        <v>-2.501668214797974</v>
+        <v>-2.778403997421265</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1830,7 +1830,7 @@
         <v>-1.5</v>
       </c>
       <c r="D62">
-        <v>0.7988709807395935</v>
+        <v>0.1047069132328033</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1844,7 +1844,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D63">
-        <v>1.378026008605957</v>
+        <v>1.253620386123657</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1858,7 +1858,7 @@
         <v>-6.400000095367432</v>
       </c>
       <c r="D64">
-        <v>-7.764408111572266</v>
+        <v>-7.60832405090332</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1872,7 +1872,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D65">
-        <v>-3.79282808303833</v>
+        <v>-3.332127809524536</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1886,7 +1886,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D66">
-        <v>1.436062335968018</v>
+        <v>2.180397748947144</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1900,7 +1900,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D67">
-        <v>-0.516477644443512</v>
+        <v>-1.380473375320435</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1914,7 +1914,7 @@
         <v>-6.699999809265137</v>
       </c>
       <c r="D68">
-        <v>-3.348042964935303</v>
+        <v>-3.835515260696411</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1928,7 +1928,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D69">
-        <v>0.5863824486732483</v>
+        <v>0.2145279049873352</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1942,7 +1942,7 @@
         <v>-7.199999809265137</v>
       </c>
       <c r="D70">
-        <v>-12.74257183074951</v>
+        <v>-8.206298828125</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1956,7 +1956,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D71">
-        <v>-2.10821008682251</v>
+        <v>-2.057340860366821</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1970,7 +1970,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D72">
-        <v>-0.48599773645401</v>
+        <v>-1.643992900848389</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1984,7 +1984,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D73">
-        <v>-2.718734741210938</v>
+        <v>1.784869194030762</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1998,7 +1998,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D74">
-        <v>2.884478569030762</v>
+        <v>3.212792634963989</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2012,7 +2012,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D75">
-        <v>1.118584156036377</v>
+        <v>0.6072824597358704</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2026,7 +2026,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D76">
-        <v>0.1113210693001747</v>
+        <v>-0.8566470742225647</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2040,7 +2040,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D77">
-        <v>1.44584584236145</v>
+        <v>1.447371244430542</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2054,7 +2054,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D78">
-        <v>-2.084764719009399</v>
+        <v>-3.126321077346802</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2068,7 +2068,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D79">
-        <v>-2.227026462554932</v>
+        <v>-3.266988515853882</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2082,7 +2082,7 @@
         <v>-7.300000190734863</v>
       </c>
       <c r="D80">
-        <v>-3.426640510559082</v>
+        <v>-4.158750057220459</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2096,7 +2096,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D81">
-        <v>-3.906652212142944</v>
+        <v>-4.165541648864746</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2110,7 +2110,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D82">
-        <v>2.838291168212891</v>
+        <v>1.972462892532349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2124,7 +2124,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D83">
-        <v>3.251907348632812</v>
+        <v>2.979060888290405</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2138,7 +2138,7 @@
         <v>-7.699999809265137</v>
       </c>
       <c r="D84">
-        <v>-3.13365650177002</v>
+        <v>-2.889314413070679</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2152,7 +2152,7 @@
         <v>-6.599999904632568</v>
       </c>
       <c r="D85">
-        <v>-8.294589996337891</v>
+        <v>-6.410872459411621</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2166,7 +2166,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D86">
-        <v>0.6437353491783142</v>
+        <v>-1.102763652801514</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2180,7 +2180,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D87">
-        <v>-2.26218843460083</v>
+        <v>-1.857526063919067</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2194,7 +2194,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D88">
-        <v>-1.286917686462402</v>
+        <v>-1.96425199508667</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2208,7 +2208,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D89">
-        <v>1.381473541259766</v>
+        <v>1.661439895629883</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2222,7 +2222,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D90">
-        <v>-3.675790071487427</v>
+        <v>-2.902382612228394</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2236,7 +2236,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D91">
-        <v>2.162510395050049</v>
+        <v>3.055303573608398</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2250,7 +2250,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D92">
-        <v>1.032587289810181</v>
+        <v>-1.686586618423462</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2264,7 +2264,7 @@
         <v>-0.5</v>
       </c>
       <c r="D93">
-        <v>0.1015296950936317</v>
+        <v>-0.8317960500717163</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2278,7 +2278,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D94">
-        <v>-5.701035976409912</v>
+        <v>-4.067008018493652</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2292,7 +2292,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D95">
-        <v>-0.8024840950965881</v>
+        <v>-1.69511342048645</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2306,7 +2306,7 @@
         <v>5</v>
       </c>
       <c r="D96">
-        <v>1.719073891639709</v>
+        <v>1.732978343963623</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2320,7 +2320,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D97">
-        <v>-0.5542201399803162</v>
+        <v>-0.99661785364151</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2334,7 +2334,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>1.065238475799561</v>
+        <v>-0.1667400747537613</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2348,7 +2348,7 @@
         <v>-3</v>
       </c>
       <c r="D99">
-        <v>-3.64105224609375</v>
+        <v>-3.303513765335083</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2362,7 +2362,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D100">
-        <v>9.204007148742676</v>
+        <v>8.550225257873535</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2376,7 +2376,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D101">
-        <v>-1.978506445884705</v>
+        <v>-2.584647178649902</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2390,7 +2390,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D102">
-        <v>2.09239935874939</v>
+        <v>2.396262168884277</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2404,7 +2404,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D103">
-        <v>-5.097675800323486</v>
+        <v>-3.810161828994751</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2418,7 +2418,7 @@
         <v>-2.799999952316284</v>
       </c>
       <c r="D104">
-        <v>-5.15706205368042</v>
+        <v>-4.9664626121521</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2432,7 +2432,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D105">
-        <v>2.38942813873291</v>
+        <v>2.368025064468384</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2446,7 +2446,7 @@
         <v>3</v>
       </c>
       <c r="D106">
-        <v>0.576701819896698</v>
+        <v>0.4145881533622742</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2460,7 +2460,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D107">
-        <v>2.309940099716187</v>
+        <v>2.201427459716797</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2474,7 +2474,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D108">
-        <v>0.7088442444801331</v>
+        <v>1.29120922088623</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2488,7 +2488,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D109">
-        <v>1.937345504760742</v>
+        <v>1.64619517326355</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2502,7 +2502,7 @@
         <v>-31</v>
       </c>
       <c r="D110">
-        <v>-21.81808471679688</v>
+        <v>-27.2000789642334</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2516,7 +2516,7 @@
         <v>-5</v>
       </c>
       <c r="D111">
-        <v>1.193353652954102</v>
+        <v>1.270710706710815</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2530,7 +2530,7 @@
         <v>-12.80000019073486</v>
       </c>
       <c r="D112">
-        <v>-14.04280281066895</v>
+        <v>-14.540207862854</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2544,7 +2544,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D113">
-        <v>2.244191884994507</v>
+        <v>-2.159600019454956</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2558,7 +2558,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D114">
-        <v>-1.488132953643799</v>
+        <v>-2.783275842666626</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2572,7 +2572,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D115">
-        <v>1.906629800796509</v>
+        <v>2.247578859329224</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2586,7 +2586,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D116">
-        <v>0.2385789453983307</v>
+        <v>1.558829545974731</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2600,7 +2600,7 @@
         <v>-3</v>
       </c>
       <c r="D117">
-        <v>-1.071790933609009</v>
+        <v>-1.121079683303833</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2614,7 +2614,7 @@
         <v>7.5</v>
       </c>
       <c r="D118">
-        <v>2.240042209625244</v>
+        <v>2.619159936904907</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2628,7 +2628,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D119">
-        <v>1.218458890914917</v>
+        <v>1.257773637771606</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2642,7 +2642,7 @@
         <v>3.5</v>
       </c>
       <c r="D120">
-        <v>2.161470413208008</v>
+        <v>2.13567042350769</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2656,7 +2656,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D121">
-        <v>-3.306115627288818</v>
+        <v>-4.131444931030273</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2670,7 +2670,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D122">
-        <v>2.247435808181763</v>
+        <v>2.210246562957764</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2684,7 +2684,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D123">
-        <v>-3.005936145782471</v>
+        <v>-2.317645072937012</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2698,7 +2698,7 @@
         <v>-1.5</v>
       </c>
       <c r="D124">
-        <v>-2.644033193588257</v>
+        <v>-2.514070272445679</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2712,7 +2712,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D125">
-        <v>-4.813084125518799</v>
+        <v>-3.766004085540771</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2726,7 +2726,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D126">
-        <v>3.247993946075439</v>
+        <v>1.744547605514526</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2740,7 +2740,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D127">
-        <v>6.74607515335083</v>
+        <v>6.40817928314209</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2754,7 +2754,7 @@
         <v>-20.20000076293945</v>
       </c>
       <c r="D128">
-        <v>-15.61678981781006</v>
+        <v>-16.04121589660645</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2768,7 +2768,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D129">
-        <v>2.16943883895874</v>
+        <v>0.6337677836418152</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2782,7 +2782,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D130">
-        <v>1.977881669998169</v>
+        <v>0.9127827286720276</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2796,7 +2796,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D131">
-        <v>1.807167649269104</v>
+        <v>1.73052978515625</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2810,7 +2810,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D132">
-        <v>-2.505485534667969</v>
+        <v>-2.859316110610962</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2824,7 +2824,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D133">
-        <v>1.889629125595093</v>
+        <v>0.03288766741752625</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2838,7 +2838,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D134">
-        <v>4.227475166320801</v>
+        <v>4.381552696228027</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2852,7 +2852,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D135">
-        <v>2.26772403717041</v>
+        <v>2.459965467453003</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2866,7 +2866,7 @@
         <v>-10.80000019073486</v>
       </c>
       <c r="D136">
-        <v>-5.011413097381592</v>
+        <v>-4.187513828277588</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2880,7 +2880,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D137">
-        <v>1.05736517906189</v>
+        <v>0.5282166004180908</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2894,7 +2894,7 @@
         <v>-9.300000190734863</v>
       </c>
       <c r="D138">
-        <v>-5.801476955413818</v>
+        <v>-5.189435958862305</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2908,7 +2908,7 @@
         <v>-32.20000076293945</v>
       </c>
       <c r="D139">
-        <v>-23.96578216552734</v>
+        <v>-25.03434181213379</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2922,7 +2922,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D140">
-        <v>1.893330812454224</v>
+        <v>2.194645643234253</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2936,7 +2936,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D141">
-        <v>-5.699624538421631</v>
+        <v>-5.803497314453125</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2950,7 +2950,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D142">
-        <v>-0.37949338555336</v>
+        <v>-1.428329229354858</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2964,7 +2964,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D143">
-        <v>1.943419933319092</v>
+        <v>1.688887357711792</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2978,7 +2978,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D144">
-        <v>-0.9098077416419983</v>
+        <v>-0.6228054761886597</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2992,7 +2992,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D145">
-        <v>0.8586629033088684</v>
+        <v>1.161154985427856</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3006,7 +3006,7 @@
         <v>-23.20000076293945</v>
       </c>
       <c r="D146">
-        <v>-17.54658889770508</v>
+        <v>-20.89251708984375</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3020,7 +3020,7 @@
         <v>-6.099999904632568</v>
       </c>
       <c r="D147">
-        <v>-2.860164880752563</v>
+        <v>-3.107158422470093</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3034,7 +3034,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D148">
-        <v>0.3189069032669067</v>
+        <v>-0.6287592649459839</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3048,7 +3048,7 @@
         <v>-2</v>
       </c>
       <c r="D149">
-        <v>-3.477189302444458</v>
+        <v>-2.869598150253296</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3062,7 +3062,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D150">
-        <v>-2.337254047393799</v>
+        <v>-2.024254322052002</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3076,7 +3076,7 @@
         <v>5.5</v>
       </c>
       <c r="D151">
-        <v>1.432313203811646</v>
+        <v>1.249321937561035</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3090,7 +3090,7 @@
         <v>4</v>
       </c>
       <c r="D152">
-        <v>2.5868821144104</v>
+        <v>2.59860372543335</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3104,7 +3104,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D153">
-        <v>2.65385913848877</v>
+        <v>1.074618101119995</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3118,7 +3118,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D154">
-        <v>-3.859029531478882</v>
+        <v>-1.829115867614746</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3132,7 +3132,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D155">
-        <v>-2.950752973556519</v>
+        <v>-2.470946073532104</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3146,7 +3146,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D156">
-        <v>2.731480121612549</v>
+        <v>2.333631277084351</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3160,7 +3160,7 @@
         <v>-8.399999618530273</v>
       </c>
       <c r="D157">
-        <v>-10.83737659454346</v>
+        <v>-9.662049293518066</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3174,7 +3174,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D158">
-        <v>-2.807525396347046</v>
+        <v>-2.751452684402466</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3188,7 +3188,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D159">
-        <v>1.58624005317688</v>
+        <v>1.022162914276123</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3202,7 +3202,7 @@
         <v>-3.5</v>
       </c>
       <c r="D160">
-        <v>-2.687606573104858</v>
+        <v>-2.686059713363647</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3216,7 +3216,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D161">
-        <v>1.121423244476318</v>
+        <v>1.534796237945557</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3230,7 +3230,7 @@
         <v>3.5</v>
       </c>
       <c r="D162">
-        <v>2.780409336090088</v>
+        <v>2.046286344528198</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3244,7 +3244,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D163">
-        <v>1.487375617027283</v>
+        <v>0.9961102604866028</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3258,7 +3258,7 @@
         <v>1.5</v>
       </c>
       <c r="D164">
-        <v>0.7432007789611816</v>
+        <v>0.8604133725166321</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3272,7 +3272,7 @@
         <v>-5.900000095367432</v>
       </c>
       <c r="D165">
-        <v>-17.39311218261719</v>
+        <v>-18.55328750610352</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3286,7 +3286,7 @@
         <v>-1</v>
       </c>
       <c r="D166">
-        <v>-1.269112348556519</v>
+        <v>-1.95439624786377</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3300,7 +3300,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D167">
-        <v>3.550272703170776</v>
+        <v>3.458417415618896</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3314,7 +3314,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D168">
-        <v>0.2292003333568573</v>
+        <v>-0.6893047690391541</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3328,7 +3328,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D169">
-        <v>1.858464121818542</v>
+        <v>1.417721509933472</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3342,7 +3342,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D170">
-        <v>-0.4743275344371796</v>
+        <v>-2.191889524459839</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3356,7 +3356,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D171">
-        <v>0.9886519312858582</v>
+        <v>0.3237159848213196</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3370,7 +3370,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D172">
-        <v>3.12126636505127</v>
+        <v>1.884037971496582</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3384,7 +3384,7 @@
         <v>3.5</v>
       </c>
       <c r="D173">
-        <v>-0.03978593274950981</v>
+        <v>-1.2216796875</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3398,7 +3398,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D174">
-        <v>2.53846287727356</v>
+        <v>1.676017045974731</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3412,7 +3412,7 @@
         <v>-21.10000038146973</v>
       </c>
       <c r="D175">
-        <v>-13.3896427154541</v>
+        <v>-14.91631984710693</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3426,7 +3426,7 @@
         <v>-5.5</v>
       </c>
       <c r="D176">
-        <v>-0.3393487334251404</v>
+        <v>-2.901083469390869</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3440,7 +3440,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D177">
-        <v>2.224203109741211</v>
+        <v>2.210855960845947</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3454,7 +3454,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D178">
-        <v>1.657212257385254</v>
+        <v>1.555468082427979</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3468,7 +3468,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D179">
-        <v>-3.617757797241211</v>
+        <v>-3.627191305160522</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3482,7 +3482,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D180">
-        <v>3.677626848220825</v>
+        <v>3.277430295944214</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3496,7 +3496,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D181">
-        <v>1.20775032043457</v>
+        <v>0.8398686051368713</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3510,7 +3510,7 @@
         <v>-1</v>
       </c>
       <c r="D182">
-        <v>-1.112290382385254</v>
+        <v>-1.905611753463745</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3524,7 +3524,7 @@
         <v>-13.30000019073486</v>
       </c>
       <c r="D183">
-        <v>-6.107545375823975</v>
+        <v>-7.067719459533691</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3538,7 +3538,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D184">
-        <v>1.266806602478027</v>
+        <v>0.7085394263267517</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3552,7 +3552,7 @@
         <v>-7.800000190734863</v>
       </c>
       <c r="D185">
-        <v>-3.307511806488037</v>
+        <v>-3.253170490264893</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3566,7 +3566,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D186">
-        <v>-3.59501838684082</v>
+        <v>-3.19365119934082</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3580,7 +3580,7 @@
         <v>0.5</v>
       </c>
       <c r="D187">
-        <v>-3.266997814178467</v>
+        <v>-3.432637929916382</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3594,7 +3594,7 @@
         <v>-7</v>
       </c>
       <c r="D188">
-        <v>-4.212772369384766</v>
+        <v>-3.712507963180542</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3608,7 +3608,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D189">
-        <v>-2.055863380432129</v>
+        <v>-1.963013887405396</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3622,7 +3622,7 @@
         <v>10.19999980926514</v>
       </c>
       <c r="D190">
-        <v>-0.9919339418411255</v>
+        <v>-1.41469931602478</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3636,7 +3636,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D191">
-        <v>-0.472484290599823</v>
+        <v>-0.9947860836982727</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3650,7 +3650,7 @@
         <v>-5.5</v>
       </c>
       <c r="D192">
-        <v>-2.331711292266846</v>
+        <v>-2.96596360206604</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3664,7 +3664,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D193">
-        <v>1.43803083896637</v>
+        <v>1.578512191772461</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3678,7 +3678,7 @@
         <v>-6.199999809265137</v>
       </c>
       <c r="D194">
-        <v>-2.275609493255615</v>
+        <v>-1.722737789154053</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3692,7 +3692,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D195">
-        <v>3.04198169708252</v>
+        <v>3.027145624160767</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3706,7 +3706,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D196">
-        <v>-2.852564811706543</v>
+        <v>-4.047820568084717</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3720,7 +3720,7 @@
         <v>-11.69999980926514</v>
       </c>
       <c r="D197">
-        <v>-5.746018886566162</v>
+        <v>-4.715161323547363</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3734,7 +3734,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D198">
-        <v>-2.604110717773438</v>
+        <v>-2.455424070358276</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3748,7 +3748,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D199">
-        <v>2.145532131195068</v>
+        <v>1.661027193069458</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3762,7 +3762,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D200">
-        <v>-0.6799365878105164</v>
+        <v>-0.8208868503570557</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3776,7 +3776,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D201">
-        <v>-0.3508580327033997</v>
+        <v>-0.8904074430465698</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3790,7 +3790,7 @@
         <v>-25.10000038146973</v>
       </c>
       <c r="D202">
-        <v>-21.02391624450684</v>
+        <v>-21.02269554138184</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3804,7 +3804,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D203">
-        <v>2.56556510925293</v>
+        <v>2.289425134658813</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3818,7 +3818,7 @@
         <v>-15.60000038146973</v>
       </c>
       <c r="D204">
-        <v>-2.99244499206543</v>
+        <v>-2.166314125061035</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3832,7 +3832,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D205">
-        <v>0.523962676525116</v>
+        <v>-0.5781437158584595</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3846,7 +3846,7 @@
         <v>-20</v>
       </c>
       <c r="D206">
-        <v>-15.54411697387695</v>
+        <v>-16.81588745117188</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3860,7 +3860,7 @@
         <v>-4.300000190734863</v>
       </c>
       <c r="D207">
-        <v>-0.5445873141288757</v>
+        <v>-1.743403911590576</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3874,7 +3874,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D208">
-        <v>-3.079466819763184</v>
+        <v>-3.114943742752075</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3888,7 +3888,7 @@
         <v>-2.5</v>
       </c>
       <c r="D209">
-        <v>1.701724052429199</v>
+        <v>1.806216478347778</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3902,7 +3902,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D210">
-        <v>-2.655325889587402</v>
+        <v>-0.8103911876678467</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3916,7 +3916,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D211">
-        <v>-4.096953868865967</v>
+        <v>-4.603806972503662</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3930,7 +3930,7 @@
         <v>1</v>
       </c>
       <c r="D212">
-        <v>-0.819518506526947</v>
+        <v>-2.106147766113281</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3944,7 +3944,7 @@
         <v>-16.60000038146973</v>
       </c>
       <c r="D213">
-        <v>-8.335605621337891</v>
+        <v>-10.45724964141846</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3958,7 +3958,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D214">
-        <v>2.519772052764893</v>
+        <v>2.337172746658325</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3972,7 +3972,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D215">
-        <v>-1.762324452400208</v>
+        <v>-0.7041974067687988</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3986,7 +3986,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D216">
-        <v>2.295375823974609</v>
+        <v>2.149937629699707</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4000,7 +4000,7 @@
         <v>-4.5</v>
       </c>
       <c r="D217">
-        <v>-4.650697231292725</v>
+        <v>-7.171299934387207</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4014,7 +4014,7 @@
         <v>2</v>
       </c>
       <c r="D218">
-        <v>1.584448575973511</v>
+        <v>1.631835460662842</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4028,7 +4028,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D219">
-        <v>-3.769612550735474</v>
+        <v>-4.587882995605469</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4042,7 +4042,7 @@
         <v>-5</v>
       </c>
       <c r="D220">
-        <v>-0.915521502494812</v>
+        <v>-0.4342473149299622</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4056,7 +4056,7 @@
         <v>2.5</v>
       </c>
       <c r="D221">
-        <v>3.51408839225769</v>
+        <v>3.175791501998901</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4070,7 +4070,7 @@
         <v>-41</v>
       </c>
       <c r="D222">
-        <v>-23.41666603088379</v>
+        <v>-24.55268478393555</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4084,7 +4084,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D223">
-        <v>-4.830820560455322</v>
+        <v>-5.013880252838135</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4098,7 +4098,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D224">
-        <v>-3.409133911132812</v>
+        <v>-3.312077283859253</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4112,7 +4112,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D225">
-        <v>0.3019894957542419</v>
+        <v>0.3199551105499268</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4126,7 +4126,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D226">
-        <v>0.9885308146476746</v>
+        <v>-0.023517906665802</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4140,7 +4140,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D227">
-        <v>5.65991735458374</v>
+        <v>6.889225959777832</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4154,7 +4154,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D228">
-        <v>-0.6338407397270203</v>
+        <v>-0.9122797250747681</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4168,7 +4168,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D229">
-        <v>-3.109769821166992</v>
+        <v>-3.29604172706604</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4182,7 +4182,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D230">
-        <v>-2.305737018585205</v>
+        <v>-2.542994737625122</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4196,7 +4196,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D231">
-        <v>-3.27007794380188</v>
+        <v>-3.833685159683228</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4210,7 +4210,7 @@
         <v>-2.5</v>
       </c>
       <c r="D232">
-        <v>-1.247449159622192</v>
+        <v>-1.992855787277222</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4224,7 +4224,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D233">
-        <v>2.574418544769287</v>
+        <v>2.741724252700806</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4238,7 +4238,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D234">
-        <v>1.359550356864929</v>
+        <v>1.339080572128296</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4252,7 +4252,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D235">
-        <v>-2.097518444061279</v>
+        <v>-3.454283475875854</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4266,7 +4266,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D236">
-        <v>0.9097814559936523</v>
+        <v>-0.03881898522377014</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4280,7 +4280,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D237">
-        <v>2.565186977386475</v>
+        <v>3.054991960525513</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4294,7 +4294,7 @@
         <v>-7.199999809265137</v>
       </c>
       <c r="D238">
-        <v>-3.469904899597168</v>
+        <v>-4.194637775421143</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4308,7 +4308,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D239">
-        <v>-1.861105918884277</v>
+        <v>-3.650441884994507</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4322,7 +4322,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D240">
-        <v>-2.519413232803345</v>
+        <v>-2.175986766815186</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4336,7 +4336,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D241">
-        <v>-1.061907529830933</v>
+        <v>-1.722903251647949</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4350,7 +4350,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D242">
-        <v>0.7339385151863098</v>
+        <v>0.4365231990814209</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4364,7 +4364,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D243">
-        <v>0.4960903227329254</v>
+        <v>0.6902063488960266</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4378,7 +4378,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D244">
-        <v>9.455532073974609</v>
+        <v>8.084807395935059</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4392,7 +4392,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D245">
-        <v>1.476074814796448</v>
+        <v>1.145108699798584</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4406,7 +4406,7 @@
         <v>-14.80000019073486</v>
       </c>
       <c r="D246">
-        <v>-13.57349395751953</v>
+        <v>-14.76318073272705</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4420,7 +4420,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D247">
-        <v>-2.774015188217163</v>
+        <v>-2.674325466156006</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4434,7 +4434,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D248">
-        <v>1.404656410217285</v>
+        <v>0.7676475644111633</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4448,7 +4448,7 @@
         <v>2</v>
       </c>
       <c r="D249">
-        <v>0.7291314601898193</v>
+        <v>0.5826305747032166</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4462,7 +4462,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D250">
-        <v>0.7334988713264465</v>
+        <v>-0.8888264894485474</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4476,7 +4476,7 @@
         <v>-3.5</v>
       </c>
       <c r="D251">
-        <v>0.06196915358304977</v>
+        <v>0.6408501267433167</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4490,7 +4490,7 @@
         <v>-8.899999618530273</v>
       </c>
       <c r="D252">
-        <v>-1.349915981292725</v>
+        <v>-3.608543395996094</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4504,7 +4504,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D253">
-        <v>2.046453714370728</v>
+        <v>1.733904838562012</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4518,7 +4518,7 @@
         <v>-15.39999961853027</v>
       </c>
       <c r="D254">
-        <v>-21.19572830200195</v>
+        <v>-20.02611923217773</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4532,7 +4532,7 @@
         <v>-33.09999847412109</v>
       </c>
       <c r="D255">
-        <v>-28.2428150177002</v>
+        <v>-27.17094421386719</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4546,7 +4546,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D256">
-        <v>-2.81955885887146</v>
+        <v>-3.088172912597656</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4560,7 +4560,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D257">
-        <v>0.2239684760570526</v>
+        <v>-0.6276619434356689</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4574,7 +4574,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D258">
-        <v>-0.3071447014808655</v>
+        <v>-0.04567110538482666</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4588,7 +4588,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D259">
-        <v>2.057041645050049</v>
+        <v>1.34538722038269</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4602,7 +4602,7 @@
         <v>-16.5</v>
       </c>
       <c r="D260">
-        <v>-6.290490627288818</v>
+        <v>-4.833512306213379</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4616,7 +4616,7 @@
         <v>-5</v>
       </c>
       <c r="D261">
-        <v>-3.16315746307373</v>
+        <v>-3.724577665328979</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4630,7 +4630,7 @@
         <v>-6</v>
       </c>
       <c r="D262">
-        <v>-2.134244441986084</v>
+        <v>-3.836900472640991</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4644,7 +4644,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D263">
-        <v>-3.727134227752686</v>
+        <v>-3.313410043716431</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4658,7 +4658,7 @@
         <v>-3.5</v>
       </c>
       <c r="D264">
-        <v>-0.1791223436594009</v>
+        <v>-1.068237781524658</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4672,7 +4672,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D265">
-        <v>0.7907761931419373</v>
+        <v>-0.01566493511199951</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4686,7 +4686,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D266">
-        <v>-3.347628593444824</v>
+        <v>-3.209448575973511</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4700,7 +4700,7 @@
         <v>5.5</v>
       </c>
       <c r="D267">
-        <v>2.535594940185547</v>
+        <v>2.511541604995728</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4714,7 +4714,7 @@
         <v>-29.20000076293945</v>
       </c>
       <c r="D268">
-        <v>-21.46393966674805</v>
+        <v>-23.39529991149902</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4728,7 +4728,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D269">
-        <v>-2.827040672302246</v>
+        <v>-2.55320143699646</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4742,7 +4742,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D270">
-        <v>-3.583280563354492</v>
+        <v>-2.788829565048218</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4756,7 +4756,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D271">
-        <v>-1.577101945877075</v>
+        <v>-1.519683122634888</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4770,7 +4770,7 @@
         <v>-10.30000019073486</v>
       </c>
       <c r="D272">
-        <v>-8.533302307128906</v>
+        <v>-9.826675415039062</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4784,7 +4784,7 @@
         <v>-7.5</v>
       </c>
       <c r="D273">
-        <v>-8.866196632385254</v>
+        <v>-9.071835517883301</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4798,7 +4798,7 @@
         <v>-3</v>
       </c>
       <c r="D274">
-        <v>-3.58708381652832</v>
+        <v>-3.016690015792847</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4812,7 +4812,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D275">
-        <v>-2.778108835220337</v>
+        <v>-3.166743040084839</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4826,7 +4826,7 @@
         <v>3.5</v>
       </c>
       <c r="D276">
-        <v>1.831628084182739</v>
+        <v>1.782411813735962</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4840,7 +4840,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D277">
-        <v>-0.7760047912597656</v>
+        <v>-0.06032150983810425</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4854,7 +4854,7 @@
         <v>3.5</v>
       </c>
       <c r="D278">
-        <v>2.733914852142334</v>
+        <v>1.864781379699707</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4868,7 +4868,7 @@
         <v>-31.29999923706055</v>
       </c>
       <c r="D279">
-        <v>-24.11307716369629</v>
+        <v>-25.75882911682129</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4882,7 +4882,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D280">
-        <v>0.5466955304145813</v>
+        <v>0.3758415579795837</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4896,7 +4896,7 @@
         <v>2</v>
       </c>
       <c r="D281">
-        <v>0.7562647461891174</v>
+        <v>0.5770693421363831</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4910,7 +4910,7 @@
         <v>1</v>
       </c>
       <c r="D282">
-        <v>-3.472796440124512</v>
+        <v>-3.184568166732788</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4924,7 +4924,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D283">
-        <v>-2.646924495697021</v>
+        <v>-2.924350738525391</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4938,7 +4938,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D284">
-        <v>1.141017913818359</v>
+        <v>0.3314486145973206</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4952,7 +4952,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D285">
-        <v>2.446096420288086</v>
+        <v>2.723613023757935</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4966,7 +4966,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D286">
-        <v>0.5658997297286987</v>
+        <v>0.4077318906784058</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4980,7 +4980,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D287">
-        <v>2.717134714126587</v>
+        <v>2.700935840606689</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4994,7 +4994,7 @@
         <v>-7</v>
       </c>
       <c r="D288">
-        <v>0.2925287783145905</v>
+        <v>-1.471384286880493</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5008,7 +5008,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D289">
-        <v>0.8947781920433044</v>
+        <v>-0.05501866340637207</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5022,7 +5022,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D290">
-        <v>2.69876766204834</v>
+        <v>2.595679998397827</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5036,7 +5036,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D291">
-        <v>-0.4467600584030151</v>
+        <v>-1.379846096038818</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5050,7 +5050,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D292">
-        <v>-3.504013776779175</v>
+        <v>-3.377056837081909</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5064,7 +5064,7 @@
         <v>7.5</v>
       </c>
       <c r="D293">
-        <v>3.7746901512146</v>
+        <v>4.07378625869751</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5078,7 +5078,7 @@
         <v>-14.89999961853027</v>
       </c>
       <c r="D294">
-        <v>-10.0079288482666</v>
+        <v>-11.26422786712646</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5092,7 +5092,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D295">
-        <v>-2.544094324111938</v>
+        <v>-2.976141452789307</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5106,7 +5106,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D296">
-        <v>1.209634065628052</v>
+        <v>0.677387535572052</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5120,7 +5120,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D297">
-        <v>-0.3196595013141632</v>
+        <v>1.073831796646118</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5134,7 +5134,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D298">
-        <v>-2.437892436981201</v>
+        <v>-2.692002058029175</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5148,7 +5148,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D299">
-        <v>2.202386140823364</v>
+        <v>2.203960657119751</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5162,7 +5162,7 @@
         <v>-30.5</v>
       </c>
       <c r="D300">
-        <v>-14.34970283508301</v>
+        <v>-16.20219230651855</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5176,7 +5176,7 @@
         <v>4.5</v>
       </c>
       <c r="D301">
-        <v>2.119890689849854</v>
+        <v>1.099066257476807</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5190,7 +5190,7 @@
         <v>-5</v>
       </c>
       <c r="D302">
-        <v>-3.27974271774292</v>
+        <v>-3.216846227645874</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5204,7 +5204,7 @@
         <v>-19.29999923706055</v>
       </c>
       <c r="D303">
-        <v>-19.55105590820312</v>
+        <v>-24.35294723510742</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5218,7 +5218,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D304">
-        <v>2.880466938018799</v>
+        <v>2.382472991943359</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5232,7 +5232,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D305">
-        <v>-1.53195595741272</v>
+        <v>-3.512148380279541</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5246,7 +5246,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D306">
-        <v>1.967043876647949</v>
+        <v>1.923733472824097</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5260,7 +5260,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D307">
-        <v>4.357627391815186</v>
+        <v>3.568035364151001</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5274,7 +5274,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D308">
-        <v>2.236548900604248</v>
+        <v>2.065827131271362</v>
       </c>
     </row>
   </sheetData>
